--- a/BWI/bestwine_output/bestwine_Montenegro.xlsx
+++ b/BWI/bestwine_output/bestwine_Montenegro.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA32"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3940,6 +3940,1388 @@
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Bar Trade</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Bar Trade</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>146213</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Bar Municipality</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Polje, Pristanska Bb</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>85000</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>https://bartrade.me</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>info@bartrade.me</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>+382 30 315 082</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>50364071</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bar-trade-horeca-centar/</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/horecacentar.montenegro/</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bartrade.horecacentar/</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>Igor Glavanovic</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igor-glavanovic-0709b0167/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Compania De Vinos Montenegro Doo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Compania De Vinos Montenegro Doo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>20547</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Morinj</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Opština Herceg Novi</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Boka Kotorska, Crna Gora</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://devinos.me</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>info@devinos.me</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>+382 32 373 170</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>50450593</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/compania.devinos.mne</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/compania_de_vinos_montenegro</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Željko Uljarević</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Director And Owner</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Compania De Vinos Montenegro Doo</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Compania De Vinos Montenegro Doo</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>20547</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Morinj</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Opština Herceg Novi</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Boka Kotorska, Crna Gora</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://devinos.me</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>info@devinos.me</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>+382 32 373 170</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>50450593</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/compania.devinos.mne</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/compania_de_vinos_montenegro</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Tamara Lazarević</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Compania De Vinos Montenegro Doo</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Compania De Vinos Montenegro Doo</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>20547</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Morinj</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Opština Herceg Novi</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Boka Kotorska, Crna Gora</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://devinos.me</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>info@devinos.me</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>+382 32 373 170</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>50450593</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/compania.devinos.mne</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/compania_de_vinos_montenegro</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Stevo Orašanin</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Montecco Inc.</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Montecco Inc.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>115352</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Danilovgrad</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Opština Danilovgrad</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Bandići Bb</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>81410</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://montecco.com</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>office@montecco.com</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 883 120</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>50048344</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/montecco-inc/</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Montecco/</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montecco.inc/</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Sandra Zdravkovic</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>Purchase Department</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sandra-zdravkovic-8b589087/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Montecco Inc.</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Montecco Inc.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>115352</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Danilovgrad</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Opština Danilovgrad</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Bandići Bb</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>81410</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://montecco.com</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>office@montecco.com</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 883 120</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>50048344</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/montecco-inc/</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Montecco/</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/montecco.inc/</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Predrag Pavlicic</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>116435</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica Municipality, Golubovci Urban Municipality</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Mahala Bb</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>81000</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klikovacdoo.com</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>info@klikovac.me</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 872 606</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>50030410</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/klikovac-doo/</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/klikovacdoo/</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Ivana Pejović</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Manager</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>116435</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica Municipality, Golubovci Urban Municipality</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Mahala Bb</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>81000</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klikovacdoo.com</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>info@klikovac.me</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 872 606</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>50030410</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/klikovac-doo/</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/klikovacdoo/</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Biljana Ceklic</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>116435</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica Municipality, Golubovci Urban Municipality</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Mahala Bb</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>81000</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klikovacdoo.com</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>info@klikovac.me</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 872 606</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>50030410</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/klikovac-doo/</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/klikovacdoo/</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Milos Klikovac</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Klikovac Doo</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>116435</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Podgorica Municipality, Golubovci Urban Municipality</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Mahala Bb</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>81000</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.klikovacdoo.com</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>info@klikovac.me</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 872 606</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>50030410</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/klikovac-doo/</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/klikovacdoo/</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Aleksandar Generalović</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Apulija Gold Wines</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Apulija Gold Wines</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>61509</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Herceg Novi</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Opština Herceg Novi</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1 Save Kovačevića</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>85340</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>novigreen.hn@gmail.com</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinoteka.Wine.Shop.Italian.Montenegro</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Primanova D.o.o.</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Primanova D.o.o.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>53881</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Opština Bar</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Vladimira Rolovića F2</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>85 000</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>http://primanova.me</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>office@primanova.me</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Jovana Vukašinović</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Ntc D.o.o</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Ntc D.o.o</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>24457</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Niksic</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Nikšić Municipality</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Veselina Masleše 13</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>81400</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://ntcshop.me</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>shop@ntc.co.me</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 221 721</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>50406751</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ntcshopmne/</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ntcshop.me</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Mladen Jovovic</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mladen-jovovic-26598677/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Voli Trade</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Voli Trade</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>103902</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Kotor</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Kotor Municipality</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Bulevar Josipa Broza bb</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://voli.me</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>webshop@voli.me</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>+382 20 445 049</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>50083264</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/voli-trade/</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Voli.Trade/</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/volivas_voli</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Bogdan Markovic</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bogdan-markovic-44a1b390</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
